--- a/Result/profitability/6191.xlsx
+++ b/Result/profitability/6191.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.72</v>
       </c>
       <c r="M2" t="n">
-        <v>1.48375</v>
+        <v>1.33625</v>
       </c>
       <c r="N2" t="n">
-        <v>19.12875</v>
+        <v>17.79375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2575</v>
+        <v>1.21625</v>
       </c>
       <c r="N3" t="n">
-        <v>16.805</v>
+        <v>15.75125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.19625</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>15.0025</v>
+        <v>14.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0125</v>
+        <v>0.9175</v>
       </c>
       <c r="N5" t="n">
-        <v>13.2675</v>
+        <v>12.5625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.82875</v>
+        <v>0.67375</v>
       </c>
       <c r="N6" t="n">
-        <v>11.28875</v>
+        <v>10.8375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6075</v>
+        <v>0.4975000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>9.641249999999999</v>
+        <v>9.38875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>0.515</v>
+        <v>0.40625</v>
       </c>
       <c r="N8" t="n">
-        <v>8.602500000000001</v>
+        <v>8.4575</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.43875</v>
       </c>
       <c r="N9" t="n">
-        <v>7.602500000000001</v>
+        <v>7.6025</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9953</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8429</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1524</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>699</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>747</v>
+      </c>
+      <c r="K75" t="n">
+        <v>361</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.48375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.865</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5471698113207548</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.159999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07043108682452937</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5135135135135136</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.639999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2692124105011933</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
